--- a/GroceryApplication/src/test/resources/TestDataSample.xlsx
+++ b/GroceryApplication/src/test/resources/TestDataSample.xlsx
@@ -5,17 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33c9259ea0c1ae4a/Desktop/javaprms/GroceryApplication/src/test/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nitha\git\GroceryApp\GroceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{2291B5D2-E99B-427A-A4D6-5E338EBAACF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94DD387A-4234-4220-B567-07F7A8CA7E08}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8FBC0B-F147-4A4B-A6CF-6F6FB4A9F871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{DBBB2AC4-E328-4831-A48C-7B76F02E2F50}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{DBBB2AC4-E328-4831-A48C-7B76F02E2F50}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
     <sheet name="ManageNewsPage" sheetId="2" r:id="rId2"/>
-    <sheet name="AdminUserPage" sheetId="3" r:id="rId3"/>
+    <sheet name="AdminUserPage" sheetId="7" r:id="rId3"/>
+    <sheet name="ManageContactPage" sheetId="3" r:id="rId4"/>
+    <sheet name="ManageFooterPage" sheetId="4" r:id="rId5"/>
+    <sheet name="ManageCategory" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>username</t>
   </si>
@@ -58,35 +61,64 @@
     <t>admin3rfw</t>
   </si>
   <si>
-    <t>Percentage Discount</t>
-  </si>
-  <si>
-    <t>Usernames</t>
-  </si>
-  <si>
-    <t>Passwords</t>
-  </si>
-  <si>
-    <t>admin985612</t>
-  </si>
-  <si>
-    <t>staff985612</t>
-  </si>
-  <si>
-    <t>Partner985612</t>
-  </si>
-  <si>
-    <t>db985612</t>
+    <t>hiiiii</t>
+  </si>
+  <si>
+    <t>sruthi@gmail.com</t>
+  </si>
+  <si>
+    <t>kizhakketharayil</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phonenumber</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Deliverytime</t>
+  </si>
+  <si>
+    <t>Deliverychargelimit</t>
+  </si>
+  <si>
+    <t>kizhakkethil</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Enter the category</t>
+  </si>
+  <si>
+    <t>staff098732</t>
+  </si>
+  <si>
+    <t>tomatos</t>
+  </si>
+  <si>
+    <t>staff098737</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -109,13 +141,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -129,10 +164,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -508,67 +539,158 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBEDD2A1-7958-4EBD-BED8-BF35481FC429}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC7E504-C5CC-4F8E-9797-EA9805BACC97}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="1" max="1" width="17.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77415437-AADF-4499-B06E-8E6250FD985A}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>762748590</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{25A5524E-31DE-403A-8EB1-8415990B570B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6748F90A-D519-454E-8A2B-BA8CC4FD002A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="20.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>765432987</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{3B98F913-615D-4C9A-AC1A-A4DEA97F3EEE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC17AC36-9281-41C3-9FF8-0B3157B6F8F3}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42204565-9158-4221-889C-87668F561E12}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
